--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -31,7 +31,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:AC1"/>
+  <x:dimension ref="A1:AC4"/>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -122,6 +122,245 @@
         <x:v>Attempt</x:v>
       </x:c>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>[EPIC_60][STORY_01][SUBSTORY_01]Holy relic description claims exclusive cleanse but OctoBogz contract completes without it</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>STORY_01</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Quests and Dialog</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>SUBSTORY_01</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Holy relic exclusivity contradiction</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>Level Design / Quests</x:v>
+      </x:c>
+      <x:c r="K2"/>
+      <x:c r="L2" t="str">
+        <x:v>res/maps/nouraajd/config.json
+res/maps/nouraajd/script.py</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>The holyRelic item description in res/maps/nouraajd/config.json reads 'A sanctified shard taken from the ruined chapel, the only tool that can cleanse the OctoBogz lair.' but the OctoBogz extermination contract completes without the relic. The onDestroy trigger for cave2 (res/maps/nouraajd/script.py:621-636 OctoBogzCaveTrigger) calls mark_octobogz_slain() and complete_octobogz_contract() unconditionally, granting the octoBogzQuest reward (1000 gold + ShadowBlade, OctoBogzQuest.onComplete). The RELIC_RETURNED check only gates the OCTOBOGZ_CLEARED flag and a flavor message (lines 631-636). A player can fully clear and be rewarded for the OctoBogz lair without ever obtaining the relic, contradicting the description's 'only tool' claim.</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>Description and mechanics agree: either (a) gate cave2 destruction/contract completion on RELIC_RETURNED so the relic is genuinely required, or (b) revise the holyRelic description to drop the exclusivity wording (e.g. 'blessed to purify the lair after the OctoBogz fall'). scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/script.py</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U2"/>
+      <x:c r="V2"/>
+      <x:c r="W2"/>
+      <x:c r="X2"/>
+      <x:c r="Y2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>[EPIC_60][STORY_01][SUBSTORY_02]OctoBogz cave described as desert sand in dialog but framed as swamp mire by surrounding signposts</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>STORY_01</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Quests and Dialog</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>SUBSTORY_02</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>OctoBogz biome continuity</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>Level Design / Quests</x:v>
+      </x:c>
+      <x:c r="K3"/>
+      <x:c r="L3" t="str">
+        <x:v>res/maps/nouraajd/dialog2.json
+res/maps/nouraajd/config.json</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>The OctoBogz refugee dialog (res/maps/nouraajd/dialog2.json) repeatedly frames the cave as desert/sand: ASK_WHY 'leave bones in the sand', ASK_ABOUT_OCTOBOGZ 'ambushing from stone and sand alike', ACCEPT_QUEST 'half-buried under boulders and sand'. But the authored ambient signposts tied to the same OctoBogz/relic plot describe a swamp/mire biome: ambientSwampFisherWarning text 'FISHER WARNING - The mire keeps nets, names, and fingers...', ambientMireLantern 'A drowned lantern burns under the swamp skin...', ambientSwampReturnScratch 'Return the relic before the mire learns your name.' Two authored sources describe the same destination as incompatible biomes (desert vs swamp). The OctoBogz are described as part octopus, consistent with the swamp framing.</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>Biome wording is consistent for the OctoBogz lair: update the dialog2.json sand/desert phrasing to mire/marsh language (or vice versa) so dialog and ambient signposts agree. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/dialog2.json</x:v>
+      </x:c>
+      <x:c r="Q3" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S3" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
+      <x:c r="Y3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB3" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>[EPIC_60][STORY_01][SUBSTORY_03]RetrieveRelicQuest reward text vaguer than the concrete greater-potion unlock it grants</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>STORY_01</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>Quests and Dialog</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>SUBSTORY_03</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>Relic quest reward wording precision</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>Improvement</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>Level Design / Quests</x:v>
+      </x:c>
+      <x:c r="K4"/>
+      <x:c r="L4" t="str">
+        <x:v>res/maps/nouraajd/script.py</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>RetrieveRelicQuest.getReward (res/maps/nouraajd/script.py:484) returns 'Unlocks stronger alchemy recipes.', but the actual grant is narrower and specific: BerenDialog.return_relic (script.py:906) sets CAN_BREW_GREATER_POTIONS, which res/config/crafting.json / res/plugins/crafting.py describe as greater-potion brewing only. The sibling DeliverLetterQuest.getReward ('Unlocks scribe-desk scroll crafting.') is precise about its CAN_CRAFT_SCROLLS unlock; the relic reward wording is comparatively vague and may lead players to expect new alchemy recipes beyond potions. The unlock fires correctly; only the player-facing text is loose.</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>RetrieveRelicQuest reward text names the concrete unlock, e.g. 'Unlocks greater potion brewing at the alchemy table.', matching CAN_BREW_GREATER_POTIONS. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/script.py</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R4" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S4" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T4" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U4"/>
+      <x:c r="V4"/>
+      <x:c r="W4"/>
+      <x:c r="X4"/>
+      <x:c r="Y4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z4" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA4" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB4" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -31,7 +31,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:AC4"/>
+  <x:dimension ref="A1:AC5"/>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -361,6 +361,85 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_01]Victor reward market redundantly stocks lesser potions already sold at the general market</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>SUBSTORY_01</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>Victor reward market potion redundancy</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>Improvement</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>Level Design / Encounters</x:v>
+      </x:c>
+      <x:c r="K5"/>
+      <x:c r="L5" t="str">
+        <x:v>res/maps/nouraajd/config.json</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>docs/nouraajd-economy.md:10 states 'Stronger Life and Mana Potions are reserved for Victor's reward market after the courtyard rescue.', framing victorMarket as the home of the stronger potions. But victorMarket.properties.items (res/maps/nouraajd/config.json) lists LesserLifePotion, LifePotion, LesserManaPotion, ManaPotion -- it also stocks the two Lesser potions the player can already buy at exampleMarket (which lists LesserLifePotion and LesserManaPotion). This dilutes the reward market's intended 'stronger potions' identity; the Lesser entries are redundant. (Same default 400g price either way, so not exploitable -- purely a content/intent inconsistency.)</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>victorMarket.items contains only the stronger potions (LifePotion, ManaPotion), matching the 'stronger ... reserved for Victor's reward market' intent in docs/nouraajd-economy.md, with the redundant LesserLifePotion/LesserManaPotion entries removed. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P5" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/docs/nouraajd-economy.md</x:v>
+      </x:c>
+      <x:c r="Q5" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R5" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S5" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T5" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U5"/>
+      <x:c r="V5"/>
+      <x:c r="W5"/>
+      <x:c r="X5"/>
+      <x:c r="Y5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z5" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA5" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB5" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -31,7 +31,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:AC5"/>
+  <x:dimension ref="A1:AC7"/>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -440,6 +440,165 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>[EPIC_60][STORY_04][SUBSTORY_01]Siege quest config carries dead objective reward hint keys shadowed by Python overrides</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>STORY_04</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Content Integrity</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>SUBSTORY_01</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>Siege quest dead config strings</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Improvement</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>Level Design / Content</x:v>
+      </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6" t="str">
+        <x:v>res/maps/siege/config.json
+res/maps/siege/script.py</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>defendSiegeQuest.properties in res/maps/siege/config.json defines objective ('Seal every siege gate with charged wands.'), reward ('500 gold and campaign completion.'), and hint ('Pritz mages carry extra wands.'). But DefendSiegeQuest in res/maps/siege/script.py (lines 50-58) overrides getObjective/getReward/getHint, and CQuest::getObjective/getReward/getHint (src/object/CQuest.cpp:38-60) return the Python override whenever one exists, falling back to the stored property only otherwise. So those three config strings are never read (dead data); only 'description' (not overridden) is used. No player-visible contradiction today because the values agree, but it is latent rot: a future edit to the config strings would have no effect and could silently diverge from the Python source of truth. The ritual map's quests already carry only 'description'.</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>defendSiegeQuest.properties contains only the keys actually consumed (description), with the dead objective/reward/hint keys removed so res/maps/siege/script.py is the single source of truth for that quest's player-facing text. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/object/CQuest.cpp</x:v>
+      </x:c>
+      <x:c r="Q6" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S6" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U6"/>
+      <x:c r="V6"/>
+      <x:c r="W6"/>
+      <x:c r="X6"/>
+      <x:c r="Y6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB6" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_02]Ritual sanctum anchor trigger omits the spawn_wave call the other two anchors perform</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>SUBSTORY_02</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Ritual sanctum anchor missing defender wave</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Improvement</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Level Design / Encounters</x:v>
+      </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
+        <x:v>res/maps/ritual/script.py</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>In res/maps/ritual/script.py the three onDestroy anchor triggers are structurally identical except for one line: AnchorNorthTrigger (lines 286-297) and AnchorCryptTrigger (lines 299-310) both call spawn_wave(game_map) before update_anchor_progress(game_map), but AnchorSanctumTrigger (lines 312-322) omits spawn_wave entirely. Destroying the north or crypt anchor spawns a defender wave; destroying the sanctum anchor does not. The anchor count still increments and the ritual/leader logic still runs, so it is not a correctness bug, but it is an authored inconsistency in difficulty pacing across the three otherwise-identical anchors.</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>The sanctum anchor's defender-wave behavior is intentional and consistent: either add spawn_wave(game_map) to AnchorSanctumTrigger to match the north/crypt anchors, or, if the omission is deliberate (final anchor, no further wave wanted), add a brief comment documenting that intent. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/ritual/script.py</x:v>
+      </x:c>
+      <x:c r="Q7" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S7" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U7"/>
+      <x:c r="V7"/>
+      <x:c r="W7"/>
+      <x:c r="X7"/>
+      <x:c r="Y7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB7" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -31,7 +31,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:AC7"/>
+  <x:dimension ref="A1:AC10"/>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -599,6 +599,245 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_03]Cave2 OctoBogz pack is a sharp early difficulty spike yet trivially skippable on cave entry</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>SUBSTORY_03</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>OctoBogz cave spike and skip</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Improvement</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Level Design / Encounters</x:v>
+      </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8" t="str">
+        <x:v>res/maps/nouraajd/config.json
+res/maps/nouraajd/script.py</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>cave2 (res/maps/nouraajd/config.json) spawns 5 OctoBogz ('monsters':'5'). Each OctoBogz (res/config/monsters.json) at load level 1 has effective stamina 10(base)+3(level)=13 -&gt; HP=stamina*7=91 (src/object/CCreature.cpp:522), damage 21-26 (base 17-21 + level 4-5), crit 22%, hit 84%. That is far above contemporaneous early monsters (Pritz/Cultist/GoblinThief ~28 HP, ~3 dmg; Gooby boss 49 HP). A non-tank class taking ~20+/round against 91 HP each is likely to die before clearing one, and the cave spawns five. Simultaneously the encounter is trivially skippable: Cave.onEnter destroys cave2 the instant the player steps on its entrance, and OctoBogzCaveTrigger (script.py:621-636) runs complete_octobogz_contract() on that onDestroy, so the player gets full quest credit (1000 gold + ShadowBlade) without fighting; the spawned OctoBogz use CRangeController targeting the cave tile and do not chase. So the marquee hard fight the designer built is both punishing if engaged and pointless to engage.</x:v>
+      </x:c>
+      <x:c r="N8" t="str">
+        <x:v>The OctoBogz encounter is tuned to be a fair, meaningful early fight: reduce OctoBogz damage (e.g. base dmgMin/dmgMax 17/21 -&gt; ~12/16) and/or stamina (10 -&gt; ~7, ~63 HP) and/or the cave2 spawn count (5 -&gt; fewer), and reconcile the 'clear the lair' contract so credit reflects actually defeating the OctoBogz rather than merely stepping on the cave. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O8" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P8" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/config/monsters.json</x:v>
+      </x:c>
+      <x:c r="Q8" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R8" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S8" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T8" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
+      <x:c r="W8"/>
+      <x:c r="X8"/>
+      <x:c r="Y8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z8" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA8" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB8" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_04]Monster fight controller auto-heal at 75 percent HP loses tempo against hard hitters</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>SUBSTORY_04</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Auto-heal tempo loss</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Improvement</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Combat AI / Balance</x:v>
+      </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9" t="str">
+        <x:v>src/core/CController.cpp</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>CMonsterFightController::control (src/core/CController.cpp:464-487) spends the whole turn using the least-powerful Heal item whenever getHpRatio() &lt; 75. A LesserLifePotion restores 20% of maxHP (potion.py healProc(power*20)=20% for power 1) = ~14 HP on a 70-HP combatant, while a hard hitter such as OctoBogz deals ~20+/round, so each auto-heal turn is a net HP loss and a tempo loss. NOTE: in normal GUI play the player's controller is replaced by CPlayerFightController at map load (src/core/CMap.cpp:124), so this affects auto-controlled creatures and headless/automated playtests rather than the human player. Surfaced during combat-balance review; this is an engine combat-AI tuning item and may be re-routed to the engine queue.</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>Auto-heal is only taken when it is a net gain / actually preserves the combatant (e.g. heal only when the strongest available heal exceeds expected incoming damage, or when below a lower threshold), so the controller does not waste turns healing 14 HP against 20+ dmg/round. Confirm via a headless fight simulation.</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>python3 game_simulation.py (headless fight scenario); python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/core/CController.cpp</x:v>
+      </x:c>
+      <x:c r="Q9" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R9" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S9" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T9" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
+      <x:c r="W9"/>
+      <x:c r="X9"/>
+      <x:c r="Y9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z9" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA9" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB9" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_05]Monster fight controller picks highest-mana interaction instead of strongest weakening caster AI</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>SUBSTORY_05</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>Caster AI picks priciest not strongest</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Combat AI / Balance</x:v>
+      </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10" t="str">
+        <x:v>src/core/CController.cpp
+res/plugins/interaction.py</x:v>
+      </x:c>
+      <x:c r="M10" t="str">
+        <x:v>CMonsterFightController::selectInteraction (src/core/CController.cpp:506-527) selects the affordable non-buff interaction with the MAXIMUM getManaCost (std::ranges::max_element by getManaCost), i.e. the priciest spell rather than the strongest. For a level-1 caster this picks MagicMissile (manaCost 5) over the basic Attack (manaCost 0), but level-1 MagicMissile deals only ~2.5 expected damage (interaction.py:98-103, a single small roll) vs ~17 for Attack. An auto-controlled caster therefore fights far below its capability (a Sorcerer auto-fighting Gooby this way wins ~0%). Masked in normal play because the player's controller is replaced by CPlayerFightController at load (CMap.cpp:124), but it degrades NPC caster behavior and any headless/automated caster playtest. NOTE: this is an engine C++ AI defect (bug-finder scope) surfaced during balance review; a controller may prefer to re-route it to the engine bug queue.</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>selectInteraction ranks candidate interactions by expected damage/value rather than by mana cost, so an auto-controlled creature uses its strongest affordable action (and level-1 MagicMissile is competitive with a basic attack or is not preferred over it). Confirm via a headless caster-vs-monster fight simulation showing the caster now wins comparably to manual play.</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>python3 game_simulation.py (headless caster fight); python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P10" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/core/CController.cpp</x:v>
+      </x:c>
+      <x:c r="Q10" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R10" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S10" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T10" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U10"/>
+      <x:c r="V10"/>
+      <x:c r="W10"/>
+      <x:c r="X10"/>
+      <x:c r="Y10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z10" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA10" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB10" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -31,7 +31,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:AC10"/>
+  <x:dimension ref="A1:AC12"/>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -838,6 +838,166 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_06]Failed crafts consume no ingredients or gold making success chance a free retry</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>SUBSTORY_06</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Crafting failure refunds everything</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Level Design / Economy</x:v>
+      </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11" t="str">
+        <x:v>res/plugins/crafting.py
+res/config/crafting.json</x:v>
+      </x:c>
+      <x:c r="M11" t="str">
+        <x:v>In apply_recipe (res/plugins/crafting.py:109-126), the success-chance roll returns on failure BEFORE any cost is paid: line 118-120 'if success_chance &lt; 100 and randint(1,100) &gt; success_chance: return _status(False, "failed")', while remove_required_items(player, recipe[inputs]) and deduct_gold(player, recipe[gold]) are at lines 122-123 (success path only). So a failed craft consumes neither ingredients nor gold -- the player simply retries for free until success. This nullifies every recipe's successChance (brew_mana_potion 95, scribe_emergency_portal_scroll 85, blend_greater_* 90, etc. in res/config/crafting.json): there is no risk or reagent cost to failure, only a wasted turn. The user-facing failure message ('The reagents fizzled and nothing was created') implies the reagents should be lost.</x:v>
+      </x:c>
+      <x:c r="N11" t="str">
+        <x:v>A failed craft costs its reagents (and optionally the gold): move remove_required_items (at least the inputs) before the success-chance roll, or consume inputs on the failure path, so successChance is a real cost/risk. A focused test crafts a &lt;100% recipe enough times to observe ingredient loss on failure. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O11" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P11" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/plugins/crafting.py</x:v>
+      </x:c>
+      <x:c r="Q11" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R11" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S11" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T11" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U11"/>
+      <x:c r="V11"/>
+      <x:c r="W11"/>
+      <x:c r="X11"/>
+      <x:c r="Y11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z11" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA11" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB11" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>[EPIC_60][STORY_02][SUBSTORY_07]Crafting cheap potions into higher-power ones and reselling is a repeatable gold exploit</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>EPIC_60</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Level Design Review</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>STORY_02</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Encounters and Balance</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>SUBSTORY_07</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Crafting-to-buyback money pump</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Level Design / Economy</x:v>
+      </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12" t="str">
+        <x:v>res/config/crafting.json
+res/config/potions.json</x:v>
+      </x:c>
+      <x:c r="M12" t="str">
+        <x:v>Several recipes turn cheap low-power inputs into a higher-power output whose vendor buyback exceeds total input cost, yielding repeatable profit. Market math (src/object/CMarket.cpp:35,43,138): price = 2^power*200 scaled by percent; player buys at sell%=100, sells back at getBuyCost = min(2^power*200*0.80, 5000) min'd with sellCost (CMarket.h:63-64). Worked example, brew_mana_potion (res/config/crafting.json): inputs 2x LesserManaPotion (potions.json power 1 -&gt; buy 400 each = 800) + 20 gold = 820 total; output ManaPotion (power 3) sells back for min(1600*0.8,5000)=1280. Net +460 per craft. LesserManaPotion is stocked (exampleMarket, victorMarket) and ManaPotion carries no 'quest' tag so it is sellable (CGameTradePanel blocks only Quest-tagged items). brew_full_life_potion / brew_full_mana_potion chains net ~+1600 (cheapest input cost ~3380/3460 vs 5000 capped buyback). The power jump (2x power-1 -&gt; power-3 for ManaPotion; 2x power-2 -&gt; power-3 GreaterLifePotion) is the root: it more than doubles value. NOTE: this contradicts an earlier review's 'no gold loop' note, which only considered buying and reselling the SAME item; the exploit is the crafting power-transformation, re-verified here against the CMarket formula. Compounded by the failed-craft-refund bug (no reagent cost on failure).</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>Total input value (ingredients + gold) is &gt;= output buyback for every craftable item, removing the positive-margin loop: lower the high output powers (ManaPotion power 3 and GreaterLifePotion power 3 are the anomalies vs their power-1/power-2 inputs), and/or raise the recipe gold costs, and/or reduce market buy%. Verify by computing buyback vs cheapest input cost for every recipe in crafting.json. scripts/validate_content.py still passes.</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>python3 scripts/validate_content.py</x:v>
+      </x:c>
+      <x:c r="P12" t="str">
+        <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/object/CMarket.cpp</x:v>
+      </x:c>
+      <x:c r="Q12" t="str">
+        <x:v>NOT_STARTED</x:v>
+      </x:c>
+      <x:c r="R12" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="S12" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T12" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="U12"/>
+      <x:c r="V12"/>
+      <x:c r="W12"/>
+      <x:c r="X12"/>
+      <x:c r="Y12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z12" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AA12" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AB12" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="AC12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -887,35 +887,37 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/plugins/crafting.py</x:v>
       </x:c>
       <x:c r="Q11" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R11" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-6</x:v>
       </x:c>
       <x:c r="S11" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T11" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U11"/>
-      <x:c r="V11"/>
-      <x:c r="W11"/>
+        <x:v>91ae0304-9e4c-4da4-81e7-2258c7cd2518</x:v>
+      </x:c>
+      <x:c r="U11" t="str">
+        <x:v>2026-06-30T22:44:18Z</x:v>
+      </x:c>
+      <x:c r="V11" t="str">
+        <x:v>2026-06-30T22:44:18Z</x:v>
+      </x:c>
+      <x:c r="W11" t="str">
+        <x:v>2026-07-01T22:44:18Z</x:v>
+      </x:c>
       <x:c r="X11"/>
       <x:c r="Y11" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z11" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AA11" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AB11" t="str">
-        <x:v/>
-      </x:c>
+        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-6</x:v>
+      </x:c>
+      <x:c r="AA11"/>
+      <x:c r="AB11"/>
       <x:c r="AC11" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -648,35 +648,37 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/config/monsters.json</x:v>
       </x:c>
       <x:c r="Q8" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R8" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-7</x:v>
       </x:c>
       <x:c r="S8" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T8" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U8"/>
-      <x:c r="V8"/>
-      <x:c r="W8"/>
+        <x:v>6d979ce2-bf9a-4641-a8b8-b9c1be61890c</x:v>
+      </x:c>
+      <x:c r="U8" t="str">
+        <x:v>2026-06-30T22:44:50Z</x:v>
+      </x:c>
+      <x:c r="V8" t="str">
+        <x:v>2026-06-30T22:44:50Z</x:v>
+      </x:c>
+      <x:c r="W8" t="str">
+        <x:v>2026-07-01T22:44:50Z</x:v>
+      </x:c>
       <x:c r="X8"/>
       <x:c r="Y8" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z8" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AA8" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AB8" t="str">
-        <x:v/>
-      </x:c>
+        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-7</x:v>
+      </x:c>
+      <x:c r="AA8"/>
+      <x:c r="AB8"/>
       <x:c r="AC8" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -971,35 +971,37 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/object/CMarket.cpp</x:v>
       </x:c>
       <x:c r="Q12" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R12" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-8</x:v>
       </x:c>
       <x:c r="S12" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T12" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U12"/>
-      <x:c r="V12"/>
-      <x:c r="W12"/>
+        <x:v>a35d6832-4950-43db-a373-de177d7d8f21</x:v>
+      </x:c>
+      <x:c r="U12" t="str">
+        <x:v>2026-06-30T22:52:14Z</x:v>
+      </x:c>
+      <x:c r="V12" t="str">
+        <x:v>2026-06-30T22:52:14Z</x:v>
+      </x:c>
+      <x:c r="W12" t="str">
+        <x:v>2026-07-01T22:52:14Z</x:v>
+      </x:c>
       <x:c r="X12"/>
       <x:c r="Y12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AA12" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AB12" t="str">
-        <x:v/>
-      </x:c>
+        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-8</x:v>
+      </x:c>
+      <x:c r="AA12"/>
+      <x:c r="AB12"/>
       <x:c r="AC12" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -171,35 +171,37 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/script.py</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R2" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-9</x:v>
       </x:c>
       <x:c r="S2" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T2" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U2"/>
-      <x:c r="V2"/>
-      <x:c r="W2"/>
+        <x:v>dc279ef7-4836-4771-9134-4dda3295c944</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>2026-06-30T22:52:55Z</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>2026-06-30T22:52:55Z</x:v>
+      </x:c>
+      <x:c r="W2" t="str">
+        <x:v>2026-07-01T22:52:55Z</x:v>
+      </x:c>
       <x:c r="X2"/>
       <x:c r="Y2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z2" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AA2" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AB2" t="str">
-        <x:v/>
-      </x:c>
+        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-9</x:v>
+      </x:c>
+      <x:c r="AA2"/>
+      <x:c r="AB2"/>
       <x:c r="AC2" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -650,7 +650,7 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/config/monsters.json</x:v>
       </x:c>
       <x:c r="Q8" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R8" t="str">
         <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-7</x:v>
@@ -665,20 +665,33 @@
         <x:v>2026-06-30T22:44:50Z</x:v>
       </x:c>
       <x:c r="V8" t="str">
-        <x:v>2026-06-30T22:44:50Z</x:v>
-      </x:c>
-      <x:c r="W8" t="str">
-        <x:v>2026-07-01T22:44:50Z</x:v>
-      </x:c>
-      <x:c r="X8"/>
+        <x:v>2026-06-30T23:06:45Z</x:v>
+      </x:c>
+      <x:c r="W8"/>
+      <x:c r="X8" t="str">
+        <x:v>2026-06-30T23:06:45Z</x:v>
+      </x:c>
       <x:c r="Y8" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z8" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-7</x:v>
-      </x:c>
-      <x:c r="AA8"/>
-      <x:c r="AB8"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA8" t="str">
+        <x:v>Tuned cave2 OctoBogz early-fight difficulty. Reduced the dedicated OctoBogz template baseStats
+(dmgMin 17-&gt;12, dmgMax 21-&gt;16, stamina 10-&gt;7 =&gt; HP 91-&gt;70, dmg 16-21) and cave2 spawn count
+(5-&gt;3) for a fair early three-mob fight, within the level-design acceptance ranges. Scoped to the
+dedicated OctoBogz type + cave2 only; crit/hit/strength/IDs/animation preserved; baseline fixture
+regenerated. Delivered via impl PR #1115. The 'trivially skippable' aspect is structural engine
+behavior (Cave.onEnter spawn + removeObjectByName fires the completion onDestroy regardless of
+kills) requiring a design decision; reported as a noted follow-up (would break authored contract tests).</x:v>
+      </x:c>
+      <x:c r="AB8" t="str">
+        <x:v>GitHub Actions impl PR #1115 (head 04b03b6): linux, linux-fast, windows, windows-deps, validate,
+export all SUCCESS (linux-coverage non-required for this data change; full linux suite passed with
+no engine-test regression). tests.test_creature_stat_scale_baseline 4 OK; scripts/validate_content.py
+passed; JSON valid; git diff --check clean.</x:v>
+      </x:c>
       <x:c r="AC8" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -171,7 +171,7 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/script.py</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R2" t="str">
         <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-9</x:v>
@@ -186,20 +186,33 @@
         <x:v>2026-06-30T22:52:55Z</x:v>
       </x:c>
       <x:c r="V2" t="str">
-        <x:v>2026-06-30T22:52:55Z</x:v>
-      </x:c>
-      <x:c r="W2" t="str">
-        <x:v>2026-07-01T22:52:55Z</x:v>
-      </x:c>
-      <x:c r="X2"/>
+        <x:v>2026-06-30T23:09:19Z</x:v>
+      </x:c>
+      <x:c r="W2"/>
+      <x:c r="X2" t="str">
+        <x:v>2026-06-30T23:09:19Z</x:v>
+      </x:c>
       <x:c r="Y2" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z2" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-9</x:v>
-      </x:c>
-      <x:c r="AA2"/>
-      <x:c r="AB2"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA2" t="str">
+        <x:v>Aligned the holyRelic item description with the actual OctoBogz contract mechanics. The
+description claimed the relic was 'the only tool that can cleanse the OctoBogz lair', but the
+cave2 OctoBogzCaveTrigger completes the extermination contract unconditionally; RELIC_RETURNED
+only gates the OCTOBOGZ_CLEARED flag and a purification flavor message (the killed-without-relic
+path is intended and tested). Chose acceptance option (b): revised the description to drop the
+false exclusivity ('blessed to purify the OctoBogz lair once the brood has fallen'), matching the
+relic's real post-clear-purification role. Description-only; no contract/trigger behavior altered.
+Delivered via impl PR #1118.</x:v>
+      </x:c>
+      <x:c r="AB2" t="str">
+        <x:v>GitHub Actions impl PR #1118 (head): linux, linux-fast, windows, windows-deps, validate, export all
+SUCCESS (linux-coverage non-required for this content change; full linux suite passed - no test
+asserts the description string). scripts/validate_content.py passed; JSON valid; git diff --check clean.</x:v>
+      </x:c>
       <x:c r="AC2" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -999,7 +999,7 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/object/CMarket.cpp</x:v>
       </x:c>
       <x:c r="Q12" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="R12" t="str">
         <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-8</x:v>
@@ -1014,20 +1014,41 @@
         <x:v>2026-06-30T22:52:14Z</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:v>2026-06-30T22:52:14Z</x:v>
-      </x:c>
-      <x:c r="W12" t="str">
-        <x:v>2026-07-01T22:52:14Z</x:v>
-      </x:c>
+        <x:v>2026-06-30T23:25:51Z</x:v>
+      </x:c>
+      <x:c r="W12"/>
       <x:c r="X12"/>
       <x:c r="Y12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-8</x:v>
-      </x:c>
-      <x:c r="AA12"/>
-      <x:c r="AB12"/>
+        <x:v>Economy fix conflicts with un-runnable/un-diagnosable engine crafting GameTests; needs native-test env or designer lever decision</x:v>
+      </x:c>
+      <x:c r="AA12" t="str">
+        <x:v>BLOCKED on native-test reconciliation. The economy analysis and fix are complete and correct at the
+data level: every craftable recipe is driven to vendor-buyback margin &lt;= 0 (verified by a new live
+invariant test tests/test_crafting_economy_no_profit.py and content_validator 111 OK). However, the
+fix cannot be landed because it repeatedly conflicts with engine-backed crafting GameTests in the
+native suite ("[test shard 2]") that THIS environment cannot run (no native _game module; submodules
+unfetchable) or diagnose (CI log retrieval returns only the cleanup tail, not the failing assertion):
+- Lever A (ManaPotion power 3-&gt;2): a real potency reduction (potion.py onUse addManaProc(power*20),
+  60-&gt;40 mana) that broke an engine GameTest asserting ManaPotion's mana/value. Reverted.
+- Lever B (raise brew_mana_potion gold 20-&gt;640): closes the +620 margin with zero potency change but
+  breaks a different engine crafting GameTest in shard 2 (specific assertion not extractable from the
+  tail-only CI log after 3 iterations).
+- The brew_full_{life,mana}_potion input swap (Greater-&gt;Max, no power change) appears test-safe and
+  fixes the two larger +2350 exploits.
+Resolution needs either a native-test-capable environment to run the failing GameTest and reconcile
+it precisely, or a designer decision on the preferred economy lever (gold vs power vs output count)
+and explicit approval to update the conflicting GameTest. Implementation PR #1119 (data + invariant
+test) is left as a starting point; do not merge until the engine test passes.</x:v>
+      </x:c>
+      <x:c r="AB12" t="str">
+        <x:v>Local validation that passed: tests.test_crafting_economy_no_profit (3 OK), tests.test_content_validator
+(111 OK), scripts/validate_content.py (passed), JSON valid, margin calc all &lt;=0, git diff --check clean.
+Blocking validation: native build workflow linux job FAILED across 3 attempts on an engine GameTest in
+"[test shard 2]" that cannot be run or diagnosed in this build-less environment.</x:v>
+      </x:c>
       <x:c r="AC12" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -917,7 +917,7 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/plugins/crafting.py</x:v>
       </x:c>
       <x:c r="Q11" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R11" t="str">
         <x:v>controller/ctrl-vm-4078-31cf30b5/subagent-6</x:v>
@@ -932,20 +932,34 @@
         <x:v>2026-06-30T22:44:18Z</x:v>
       </x:c>
       <x:c r="V11" t="str">
-        <x:v>2026-06-30T22:44:18Z</x:v>
-      </x:c>
-      <x:c r="W11" t="str">
-        <x:v>2026-07-01T22:44:18Z</x:v>
-      </x:c>
-      <x:c r="X11"/>
+        <x:v>2026-06-30T23:32:34Z</x:v>
+      </x:c>
+      <x:c r="W11"/>
+      <x:c r="X11" t="str">
+        <x:v>2026-06-30T23:32:34Z</x:v>
+      </x:c>
       <x:c r="Y11" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z11" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4078-31cf30b5/subagent-6</x:v>
-      </x:c>
-      <x:c r="AA11"/>
-      <x:c r="AB11"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA11" t="str">
+        <x:v>Fixed the free-retry crafting exploit. apply_recipe (res/plugins/crafting.py) returned on the
+success-chance failure roll BEFORE paying any cost, so a failed craft consumed nothing. Hoisted
+remove_required_items + deduct_gold above the roll (after the existing inventory/gold precondition
+gates that still guard both paths), so a failed craft now costs its inputs and gold while withholding
+outputs; the success path is behaviorally unchanged. Added tests/regression/test_crafting_failure_cost.py
+(4 tests) and reconciled the existing test_crafting_transactions_are_atomic RNG-failure section to the
+corrected, still-atomic contract (verified no design-intent for free-on-failure; recipes' 95/90/85
+successChance values are only meaningful with a failure cost). Delivered via impl PR #1114.</x:v>
+      </x:c>
+      <x:c r="AB11" t="str">
+        <x:v>GitHub Actions impl PR #1114 (head 02ae980): linux, linux-fast, windows, windows-deps, linux-coverage,
+validate, export all SUCCESS (coverage required for the crafting.py code change; full native GameTest
+suite including the reconciled atomic test passed). Local: tests.regression.test_crafting_failure_cost
+4 OK (sensitivity-checked against pre-fix source); py_compile + git diff --check clean.</x:v>
+      </x:c>
       <x:c r="AC11" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -583,35 +583,41 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/ritual/script.py</x:v>
       </x:c>
       <x:c r="Q7" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R7" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-5484-a0eec458/subagent-ritualwave</x:v>
       </x:c>
       <x:c r="S7" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T7" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U7"/>
-      <x:c r="V7"/>
+        <x:v>87b96ef1-428c-4552-b9fc-f70e2f8230e3</x:v>
+      </x:c>
+      <x:c r="U7" t="str">
+        <x:v>2026-07-01T17:22:43Z</x:v>
+      </x:c>
+      <x:c r="V7" t="str">
+        <x:v>2026-07-01T17:23:21Z</x:v>
+      </x:c>
       <x:c r="W7"/>
-      <x:c r="X7"/>
+      <x:c r="X7" t="str">
+        <x:v>2026-07-01T17:23:21Z</x:v>
+      </x:c>
       <x:c r="Y7" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z7" t="str">
-        <x:v/>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="AA7" t="str">
-        <x:v/>
+        <x:v>Fixed the parallel-structure defect: AnchorSanctumTrigger.trigger now calls spawn_wave(game_map) between showMessage and update_anchor_progress, exactly like AnchorNorthTrigger and AnchorCryptTrigger. Destroying the sanctum anchor now spawns a defensive wave like the other two anchors, restoring consistent escalation. One-line addition; no id/behavior renames.</x:v>
       </x:c>
       <x:c r="AB7" t="str">
-        <x:v/>
+        <x:v>python ast parse OK; validate_content passes; no ritual test counts wave monsters (test_ritual_quest_requires_successful_disruption / test_ritual_happy_path_frees_captive_and_starts_siege assert only flags/gold/quests/transition), so behavior-consistent fix needs no test change. Full native CI (build + campaign gates + C++) to confirm the ritual walkthrough on merge.</x:v>
       </x:c>
       <x:c r="AC7" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -504,35 +504,41 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/object/CQuest.cpp</x:v>
       </x:c>
       <x:c r="Q6" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R6" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-5484-a0eec458/subagent-siegecfg</x:v>
       </x:c>
       <x:c r="S6" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T6" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U6"/>
-      <x:c r="V6"/>
+        <x:v>7ac48f0a-5625-4e21-8541-38f0ab0261ec</x:v>
+      </x:c>
+      <x:c r="U6" t="str">
+        <x:v>2026-07-01T17:53:13Z</x:v>
+      </x:c>
+      <x:c r="V6" t="str">
+        <x:v>2026-07-01T17:53:58Z</x:v>
+      </x:c>
       <x:c r="W6"/>
-      <x:c r="X6"/>
+      <x:c r="X6" t="str">
+        <x:v>2026-07-01T17:53:58Z</x:v>
+      </x:c>
       <x:c r="Y6" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z6" t="str">
-        <x:v/>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="AA6" t="str">
-        <x:v/>
+        <x:v>Removed the dead objective/reward/hint keys from defendSiegeQuest.properties in res/maps/siege/config.json, leaving only the consumed 'description'. DefendSiegeQuest in siege/script.py overrides getObjective/getReward/getHint, and CQuest returns the Python override whenever one exists, so those three config strings were never read. res/maps/siege/script.py is now the single source of truth for that quest's objective/reward/hint text. Values were identical, so no player-visible change. Behavior-preserving.</x:v>
       </x:c>
       <x:c r="AB6" t="str">
-        <x:v/>
+        <x:v>python json parse OK; validate_content passes (siege map still valid); no test references the removed config keys. Native campaign gate (siege walkthrough) confirms on CI.</x:v>
       </x:c>
       <x:c r="AC6" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -345,35 +345,41 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/script.py</x:v>
       </x:c>
       <x:c r="Q4" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R4" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-5484-a0eec458/subagent-relictext</x:v>
       </x:c>
       <x:c r="S4" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T4" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U4"/>
-      <x:c r="V4"/>
+        <x:v>153759b1-a20d-492d-b056-a8c7ca523567</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:v>2026-07-01T18:01:39Z</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>2026-07-01T18:02:48Z</x:v>
+      </x:c>
       <x:c r="W4"/>
-      <x:c r="X4"/>
+      <x:c r="X4" t="str">
+        <x:v>2026-07-01T18:02:48Z</x:v>
+      </x:c>
       <x:c r="Y4" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z4" t="str">
-        <x:v/>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="AA4" t="str">
-        <x:v/>
+        <x:v>RetrieveRelicQuest.getReward now returns 'Unlocks greater potion brewing at the alchemy table.' (was the vague 'Unlocks stronger alchemy recipes.'), naming the concrete CAN_BREW_GREATER_POTIONS unlock that BerenDialog.return_relic sets. Player-facing text only; the unlock behavior is unchanged.</x:v>
       </x:c>
       <x:c r="AB4" t="str">
-        <x:v/>
+        <x:v>validate_content passes; script.py parses.</x:v>
       </x:c>
       <x:c r="AC4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -424,35 +430,41 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/docs/nouraajd-economy.md</x:v>
       </x:c>
       <x:c r="Q5" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R5" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-5484-a0eec458/subagent-victormkt</x:v>
       </x:c>
       <x:c r="S5" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T5" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U5"/>
-      <x:c r="V5"/>
+        <x:v>53288d1c-a7b8-4149-bf2e-070b2714ce82</x:v>
+      </x:c>
+      <x:c r="U5" t="str">
+        <x:v>2026-07-01T18:01:39Z</x:v>
+      </x:c>
+      <x:c r="V5" t="str">
+        <x:v>2026-07-01T18:02:48Z</x:v>
+      </x:c>
       <x:c r="W5"/>
-      <x:c r="X5"/>
+      <x:c r="X5" t="str">
+        <x:v>2026-07-01T18:02:48Z</x:v>
+      </x:c>
       <x:c r="Y5" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z5" t="str">
-        <x:v/>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="AA5" t="str">
-        <x:v/>
+        <x:v>victorMarket.items now lists only the stronger potions (LifePotion, ManaPotion); the redundant LesserLifePotion/LesserManaPotion entries (already sold at exampleMarket) are removed, matching the documented intent in docs/nouraajd-economy.md that stronger potions are reserved for Victor's reward market. Same 400g price and still available at the general market, so no functional/economy change.</x:v>
       </x:c>
       <x:c r="AB5" t="str">
-        <x:v/>
+        <x:v>validate_content passes; config valid JSON.</x:v>
       </x:c>
       <x:c r="AC5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -266,35 +266,41 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/res/maps/nouraajd/dialog2.json</x:v>
       </x:c>
       <x:c r="Q3" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R3" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-5484-a0eec458/subagent-biome</x:v>
       </x:c>
       <x:c r="S3" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T3" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U3"/>
-      <x:c r="V3"/>
+        <x:v>42fe2c78-e052-4211-b83c-c5e9fad1a47b</x:v>
+      </x:c>
+      <x:c r="U3" t="str">
+        <x:v>2026-07-01T18:10:39Z</x:v>
+      </x:c>
+      <x:c r="V3" t="str">
+        <x:v>2026-07-01T18:11:56Z</x:v>
+      </x:c>
       <x:c r="W3"/>
-      <x:c r="X3"/>
+      <x:c r="X3" t="str">
+        <x:v>2026-07-01T18:11:56Z</x:v>
+      </x:c>
       <x:c r="Y3" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z3" t="str">
-        <x:v/>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="AA3" t="str">
-        <x:v/>
+        <x:v>Made the OctoBogz lair biome wording consistent with the authored majority. The three ambient signposts (ambientSwampFisherWarning/ambientMireLantern/ambientSwampReturnScratch) and the part-octopus OctoBogz establish a swamp/mire biome; the dialog2.json desert/sand phrasings were the outliers. Reworded them to swamp language: 'leave bones in the sand'-&gt;'in the mire'; 'ambushing from stone and sand alike'-&gt;'from reed and mud alike'; 'half-buried under boulders and sand'-&gt;'half-sunk under boulders and silt' (both occurrences). The dialog already says 'east across the river', which the swamp framing fits. Dialog ids/options/state machine unchanged; text only.</x:v>
       </x:c>
       <x:c r="AB3" t="str">
-        <x:v/>
+        <x:v>dialog2.json valid JSON; no sand/desert/dune references remain; validate_content passes.</x:v>
       </x:c>
       <x:c r="AC3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -787,35 +787,37 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/core/CController.cpp</x:v>
       </x:c>
       <x:c r="Q9" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R9" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-43</x:v>
       </x:c>
       <x:c r="S9" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U9"/>
-      <x:c r="V9"/>
-      <x:c r="W9"/>
+        <x:v>e7c49716-ece9-4c1b-bd7b-5228562cc07c</x:v>
+      </x:c>
+      <x:c r="U9" t="str">
+        <x:v>2026-07-03T03:57:13Z</x:v>
+      </x:c>
+      <x:c r="V9" t="str">
+        <x:v>2026-07-03T03:57:13Z</x:v>
+      </x:c>
+      <x:c r="W9" t="str">
+        <x:v>2026-07-03T07:57:13Z</x:v>
+      </x:c>
       <x:c r="X9"/>
       <x:c r="Y9" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AA9" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AB9" t="str">
-        <x:v/>
-      </x:c>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-43</x:v>
+      </x:c>
+      <x:c r="AA9"/>
+      <x:c r="AB9"/>
       <x:c r="AC9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -867,35 +869,37 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/core/CController.cpp</x:v>
       </x:c>
       <x:c r="Q10" t="str">
-        <x:v>NOT_STARTED</x:v>
+        <x:v>IN_PROGRESS</x:v>
       </x:c>
       <x:c r="R10" t="str">
-        <x:v/>
+        <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-44</x:v>
       </x:c>
       <x:c r="S10" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="T10" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="U10"/>
-      <x:c r="V10"/>
-      <x:c r="W10"/>
+        <x:v>6477ddb0-6608-4317-9f5f-a250288f6658</x:v>
+      </x:c>
+      <x:c r="U10" t="str">
+        <x:v>2026-07-03T03:57:13Z</x:v>
+      </x:c>
+      <x:c r="V10" t="str">
+        <x:v>2026-07-03T03:57:13Z</x:v>
+      </x:c>
+      <x:c r="W10" t="str">
+        <x:v>2026-07-03T07:57:13Z</x:v>
+      </x:c>
       <x:c r="X10"/>
       <x:c r="Y10" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z10" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AA10" t="str">
-        <x:v/>
-      </x:c>
-      <x:c r="AB10" t="str">
-        <x:v/>
-      </x:c>
+        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-44</x:v>
+      </x:c>
+      <x:c r="AA10"/>
+      <x:c r="AB10"/>
       <x:c r="AC10" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -787,7 +787,7 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/core/CController.cpp</x:v>
       </x:c>
       <x:c r="Q9" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R9" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-43</x:v>
@@ -802,20 +802,24 @@
         <x:v>2026-07-03T03:57:13Z</x:v>
       </x:c>
       <x:c r="V9" t="str">
-        <x:v>2026-07-03T03:57:13Z</x:v>
-      </x:c>
-      <x:c r="W9" t="str">
-        <x:v>2026-07-03T07:57:13Z</x:v>
-      </x:c>
-      <x:c r="X9"/>
+        <x:v>2026-07-03T04:55:20Z</x:v>
+      </x:c>
+      <x:c r="W9"/>
+      <x:c r="X9" t="str">
+        <x:v>2026-07-03T04:55:20Z</x:v>
+      </x:c>
       <x:c r="Y9" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z9" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-43</x:v>
-      </x:c>
-      <x:c r="AA9"/>
-      <x:c r="AB9"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA9" t="str">
+        <x:v>Gated CMonsterFightController auto-heal on net tempo (heal_preserves_combatant): emergency + net-gain heuristics replace the fixed 75%-HP trigger; added 3 controller unit tests. Delivered by PR #1337 (merged to main).</x:v>
+      </x:c>
+      <x:c r="AB9" t="str">
+        <x:v>PR #1337 CI green (full build + unit lanes); squash-merged to main at 6d8ee346.</x:v>
+      </x:c>
       <x:c r="AC9" t="n">
         <x:v>1</x:v>
       </x:c>

--- a/planning/fall_of_nouraajd_level_design_proposals.xlsx
+++ b/planning/fall_of_nouraajd_level_design_proposals.xlsx
@@ -873,7 +873,7 @@
         <x:v>https://github.com/lisu188/fall-of-nouraajd/blob/main/src/core/CController.cpp</x:v>
       </x:c>
       <x:c r="Q10" t="str">
-        <x:v>IN_PROGRESS</x:v>
+        <x:v>DONE</x:v>
       </x:c>
       <x:c r="R10" t="str">
         <x:v>controller/ctrl-vm-4039-a70f65a5/subagent-44</x:v>
@@ -888,20 +888,24 @@
         <x:v>2026-07-03T03:57:13Z</x:v>
       </x:c>
       <x:c r="V10" t="str">
-        <x:v>2026-07-03T03:57:13Z</x:v>
-      </x:c>
-      <x:c r="W10" t="str">
-        <x:v>2026-07-03T07:57:13Z</x:v>
-      </x:c>
-      <x:c r="X10"/>
+        <x:v>2026-07-03T09:06:51Z</x:v>
+      </x:c>
+      <x:c r="W10"/>
+      <x:c r="X10" t="str">
+        <x:v>2026-07-03T09:06:51Z</x:v>
+      </x:c>
       <x:c r="Y10" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="Z10" t="str">
-        <x:v>Claimed by controller/ctrl-vm-4039-a70f65a5/subagent-44</x:v>
-      </x:c>
-      <x:c r="AA10"/>
-      <x:c r="AB10"/>
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="AA10" t="str">
+        <x:v>Replaced highest-mana interaction pick with a deterministic weakening-value ranking (expected hit + sustained opponent debuff over duration), mana affordability respected, ties toward cheaper spell. Delivered by PR #1352 (merged to main).</x:v>
+      </x:c>
+      <x:c r="AB10" t="str">
+        <x:v>PR #1352 CI green after rebase onto post-Wardens-Road main; squash-merged to main at 07:48Z.</x:v>
+      </x:c>
       <x:c r="AC10" t="n">
         <x:v>1</x:v>
       </x:c>
